--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136020383</v>
       </c>
       <c r="B5" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
